--- a/artfynd/A 2463-2026 artfynd.xlsx
+++ b/artfynd/A 2463-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105937888</v>
+        <v>105937627</v>
       </c>
       <c r="B2" t="n">
-        <v>5112</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467292.8442629401</v>
+        <v>467254</v>
       </c>
       <c r="R2" t="n">
-        <v>6241180.684547017</v>
+        <v>6241130</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +752,14 @@
           <t>2022-04-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-21</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre gnagspår och kläckhål på grenar 3-4 m upp på levande gran.</t>
+          <t>Äldre gnagspår och kläckhål på liggande del av knäckt gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105937627</v>
+        <v>105937888</v>
       </c>
       <c r="B3" t="n">
-        <v>5112</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467254.6604637058</v>
+        <v>467293</v>
       </c>
       <c r="R3" t="n">
-        <v>6241129.401761469</v>
+        <v>6241181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,24 +864,14 @@
           <t>2022-04-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre gnagspår och kläckhål på liggande del av knäckt gran.</t>
+          <t>Äldre gnagspår och kläckhål på grenar 3-4 m upp på levande gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,6 +896,118 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>105938074</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brokamåla Spydammsgylet, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>467365</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6241463</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Olofström</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jämshög</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår och kläckhål på vindfälle gran. Många kläckhål.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
